--- a/output/RecommendedOrder.xlsx
+++ b/output/RecommendedOrder.xlsx
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr"/>
     </row>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="inlineStr"/>
     </row>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C16" t="inlineStr"/>
     </row>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C17" t="inlineStr"/>
     </row>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C24" t="inlineStr"/>
     </row>
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="C26" t="inlineStr"/>
     </row>
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="inlineStr"/>
     </row>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C29" t="inlineStr"/>
     </row>
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="C30" t="inlineStr"/>
     </row>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C33" t="inlineStr"/>
     </row>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C35" t="inlineStr"/>
     </row>
@@ -901,7 +901,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C41" t="inlineStr"/>
     </row>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="C44" t="inlineStr"/>
     </row>
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="C50" t="inlineStr"/>
     </row>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C53" t="inlineStr"/>
     </row>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C54" t="inlineStr"/>
     </row>
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="C56" t="inlineStr"/>
     </row>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C64" t="inlineStr"/>
     </row>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C70" t="inlineStr"/>
     </row>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C74" t="inlineStr"/>
     </row>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C75" t="inlineStr"/>
     </row>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C83" t="inlineStr"/>
     </row>
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C86" t="inlineStr"/>
     </row>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C88" t="inlineStr"/>
     </row>
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C89" t="inlineStr"/>
     </row>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C90" t="inlineStr"/>
     </row>
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C92" t="inlineStr"/>
     </row>
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C93" t="inlineStr"/>
     </row>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C98" t="inlineStr"/>
     </row>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C99" t="inlineStr"/>
     </row>
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C103" t="inlineStr"/>
     </row>
@@ -1637,7 +1637,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C105" t="inlineStr"/>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C107" t="inlineStr"/>
     </row>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C108" t="inlineStr"/>
     </row>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C110" t="inlineStr"/>
     </row>
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C113" t="inlineStr"/>
     </row>
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C115" t="inlineStr"/>
     </row>
@@ -1758,7 +1758,7 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C116" t="inlineStr"/>
     </row>
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C119" t="inlineStr"/>
     </row>
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C125" t="inlineStr"/>
     </row>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C128" t="inlineStr"/>
     </row>
@@ -1920,7 +1920,7 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C130" t="inlineStr"/>
     </row>
@@ -1931,7 +1931,7 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C131" t="inlineStr"/>
     </row>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C137" t="inlineStr"/>
     </row>
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C138" t="inlineStr"/>
     </row>
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C147" t="inlineStr"/>
     </row>
@@ -2129,7 +2129,7 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C149" t="inlineStr"/>
     </row>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C151" t="inlineStr"/>
     </row>
@@ -2236,7 +2236,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C158" t="inlineStr"/>
     </row>
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C161" t="inlineStr"/>
     </row>
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C162" t="inlineStr"/>
     </row>
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C164" t="inlineStr"/>
     </row>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="C166" t="inlineStr"/>
     </row>
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C173" t="inlineStr"/>
     </row>
@@ -2423,7 +2423,7 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C175" t="inlineStr"/>
     </row>
@@ -2493,7 +2493,7 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C181" t="inlineStr"/>
     </row>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C182" t="inlineStr"/>
     </row>
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="C183" t="inlineStr"/>
     </row>
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C186" t="inlineStr"/>
     </row>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C191" t="inlineStr"/>
     </row>
@@ -2614,7 +2614,7 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C192" t="inlineStr"/>
     </row>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C195" t="inlineStr"/>
     </row>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C198" t="inlineStr"/>
     </row>

--- a/output/RecommendedOrder.xlsx
+++ b/output/RecommendedOrder.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr"/>
     </row>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" t="inlineStr"/>
     </row>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C24" t="inlineStr"/>
     </row>
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C26" t="inlineStr"/>
     </row>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29" t="inlineStr"/>
     </row>
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C30" t="inlineStr"/>
     </row>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C33" t="inlineStr"/>
     </row>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C35" t="inlineStr"/>
     </row>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C44" t="inlineStr"/>
     </row>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C47" t="inlineStr"/>
     </row>
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C50" t="inlineStr"/>
     </row>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C53" t="inlineStr"/>
     </row>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C54" t="inlineStr"/>
     </row>
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C56" t="inlineStr"/>
     </row>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C70" t="inlineStr"/>
     </row>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C74" t="inlineStr"/>
     </row>
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C86" t="inlineStr"/>
     </row>
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C89" t="inlineStr"/>
     </row>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C90" t="inlineStr"/>
     </row>
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C92" t="inlineStr"/>
     </row>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C98" t="inlineStr"/>
     </row>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C99" t="inlineStr"/>
     </row>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C102" t="inlineStr"/>
     </row>
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C103" t="inlineStr"/>
     </row>
@@ -1637,7 +1637,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C105" t="inlineStr"/>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C107" t="inlineStr"/>
     </row>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C108" t="inlineStr"/>
     </row>
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C115" t="inlineStr"/>
     </row>
@@ -1758,7 +1758,7 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C116" t="inlineStr"/>
     </row>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C128" t="inlineStr"/>
     </row>
@@ -1920,7 +1920,7 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C130" t="inlineStr"/>
     </row>
@@ -1986,7 +1986,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C136" t="inlineStr"/>
     </row>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C137" t="inlineStr"/>
     </row>
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C138" t="inlineStr"/>
     </row>
@@ -2129,7 +2129,7 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C149" t="inlineStr"/>
     </row>
@@ -2236,7 +2236,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C158" t="inlineStr"/>
     </row>
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C161" t="inlineStr"/>
     </row>
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C162" t="inlineStr"/>
     </row>
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C164" t="inlineStr"/>
     </row>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C166" t="inlineStr"/>
     </row>
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C170" t="inlineStr"/>
     </row>
@@ -2493,7 +2493,7 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C181" t="inlineStr"/>
     </row>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C182" t="inlineStr"/>
     </row>
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C183" t="inlineStr"/>
     </row>
@@ -2581,7 +2581,7 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C189" t="inlineStr"/>
     </row>
@@ -2614,7 +2614,7 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C192" t="inlineStr"/>
     </row>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C194" t="inlineStr"/>
     </row>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C195" t="inlineStr"/>
     </row>
